--- a/Reports/AreDifferent/decryption_canalisation_byHouse2/decryption_canalisation_byHouse2.xlsx
+++ b/Reports/AreDifferent/decryption_canalisation_byHouse2/decryption_canalisation_byHouse2.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20827"/>
   <workbookPr codeName="ThisWorkbook"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\OpenServer\domains\REPORTS\Reports\AreDifferent\decryption_canalisation_byHouse2\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7295C73-DB97-4C55-A9E6-9ED553C9C45A}" xr6:coauthVersionLast="37" xr6:coauthVersionMax="37" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23385" yWindow="735" windowWidth="24615" windowHeight="17025"/>
+    <workbookView xWindow="23385" yWindow="735" windowWidth="24615" windowHeight="17025" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Worksheet" sheetId="1" r:id="rId1"/>
@@ -14,13 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="174">
-  <si>
-    <t>Утверждаю :</t>
-  </si>
-  <si>
-    <t xml:space="preserve">по жилищно-коммунальному хозяйству </t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="262" uniqueCount="166">
   <si>
     <t>ООО "ЭнергоКомпания"</t>
   </si>
@@ -59,21 +59,6 @@
   </si>
   <si>
     <t xml:space="preserve"> в том числеРСО гвс</t>
-  </si>
-  <si>
-    <t>Подписи  :</t>
-  </si>
-  <si>
-    <t>Производитель:</t>
-  </si>
-  <si>
-    <t>Служба:</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Директор МКУ "СЗ ЖКХ" </t>
-  </si>
-  <si>
-    <t>______________________ Д.В.Игошин</t>
   </si>
   <si>
     <t>Нач.ПЭО________________ Л.Д.Сафонова</t>
@@ -496,12 +481,6 @@
   </si>
   <si>
     <t>"за ".$this-&gt;H['full_name_month']</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> ______________ Д.А.Соловьев</t>
-  </si>
-  <si>
-    <t>______________М.Е.Праздников</t>
   </si>
   <si>
     <t>Справка по расчету субсидий на водоотведение</t>
@@ -526,37 +505,40 @@
     </r>
   </si>
   <si>
-    <t>Зам.директора по экономике</t>
-  </si>
-  <si>
-    <t>Главный инженер</t>
-  </si>
-  <si>
-    <t>______________Е.А.Сикова</t>
-  </si>
-  <si>
-    <t>Вед.специалист по ВКХ_______________Н.А.Крюкова</t>
-  </si>
-  <si>
-    <t>И. о. заместителя Главы Беловского городского округа</t>
-  </si>
-  <si>
-    <t>(на осн.доверенности № 1/6733-8 от 13.12.2024)</t>
-  </si>
-  <si>
-    <t>___________________   Е.Т. Муратов</t>
-  </si>
-  <si>
-    <t>"______"_________________   2025</t>
-  </si>
-  <si>
-    <t>Приложение  к Соглашению № 30-юр  с 29.01.2025</t>
+    <t>Получатель субсидии:</t>
+  </si>
+  <si>
+    <t>Генеральный директор ООО"ЭК"________________ Игошин Д.В.</t>
+  </si>
+  <si>
+    <t>Вед.специалист по ВКХ________________ Н.А.Крюкова</t>
+  </si>
+  <si>
+    <t>Распорядитель субсидии:</t>
+  </si>
+  <si>
+    <t>Начальник УЖКиДК АБГО</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> ______________ Соловьев Д.А.</t>
+  </si>
+  <si>
+    <t>Начальник ПТО</t>
+  </si>
+  <si>
+    <t>______________Кочегаров Д.В.</t>
+  </si>
+  <si>
+    <t>Начальник ПЭО</t>
+  </si>
+  <si>
+    <t>______________Праздников М.Е.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
     <numFmt numFmtId="164" formatCode="0.000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
@@ -564,7 +546,7 @@
     <numFmt numFmtId="167" formatCode="#,##0.0000_ ;[Red]\-#,##0.0000\ "/>
     <numFmt numFmtId="168" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="30" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
@@ -1411,98 +1393,43 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="4" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="6" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1529,33 +1456,88 @@
     <xf numFmtId="0" fontId="3" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="6" fillId="9" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="26" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="4" fontId="6" fillId="8" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
-    <cellStyle name="Обычный 2" xfId="1"/>
-    <cellStyle name="Обычный 3" xfId="2"/>
-    <cellStyle name="Обычный_Водичка с 01.05. 2009г" xfId="3"/>
+    <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
+    <cellStyle name="Обычный 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
+    <cellStyle name="Обычный_Водичка с 01.05. 2009г" xfId="3" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9"/>
@@ -1567,6 +1549,14 @@
       <color rgb="FFCCECFF"/>
     </mruColors>
   </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -1856,12 +1846,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:BN38"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5.42578125" customWidth="1"/>
     <col min="2" max="2" width="24.5703125" customWidth="1"/>
@@ -1874,24 +1864,24 @@
     <col min="42" max="55" width="9.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" s="11" customFormat="1">
+    <row r="1" spans="1:60" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="BD1" s="11" t="s">
-        <v>40</v>
+        <v>33</v>
       </c>
       <c r="BE1" s="11" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="BF1" s="11" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="BG1" s="11">
         <v>20</v>
       </c>
       <c r="BH1" s="11" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:60" s="11" customFormat="1" ht="18.75">
+    <row r="2" spans="1:60" s="11" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A2" s="85"/>
       <c r="B2" s="85"/>
       <c r="C2" s="85"/>
@@ -1926,7 +1916,7 @@
       <c r="AG2" s="89"/>
       <c r="AH2" s="89"/>
     </row>
-    <row r="3" spans="1:60" s="11" customFormat="1" ht="18.75">
+    <row r="3" spans="1:60" s="11" customFormat="1" ht="18.75" x14ac:dyDescent="0.25">
       <c r="A3" s="85"/>
       <c r="B3" s="85"/>
       <c r="C3" s="85"/>
@@ -1948,9 +1938,7 @@
       <c r="T3" s="85"/>
       <c r="U3" s="85"/>
       <c r="V3" s="85"/>
-      <c r="W3" s="91" t="s">
-        <v>173</v>
-      </c>
+      <c r="W3" s="91"/>
       <c r="X3" s="85"/>
       <c r="Y3" s="85"/>
       <c r="Z3" s="85"/>
@@ -1963,7 +1951,7 @@
       <c r="AG3" s="85"/>
       <c r="AH3" s="85"/>
     </row>
-    <row r="4" spans="1:60" s="11" customFormat="1">
+    <row r="4" spans="1:60" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="85"/>
       <c r="B4" s="85"/>
       <c r="C4" s="85"/>
@@ -1997,7 +1985,7 @@
       <c r="AG4" s="92"/>
       <c r="AH4" s="92"/>
     </row>
-    <row r="5" spans="1:60" s="11" customFormat="1" ht="18.75">
+    <row r="5" spans="1:60" s="11" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A5" s="85"/>
       <c r="B5" s="85"/>
       <c r="C5" s="85"/>
@@ -2018,9 +2006,7 @@
       <c r="T5" s="16"/>
       <c r="U5" s="16"/>
       <c r="V5" s="92"/>
-      <c r="W5" s="94" t="s">
-        <v>0</v>
-      </c>
+      <c r="W5" s="94"/>
       <c r="X5" s="92"/>
       <c r="Y5" s="92"/>
       <c r="Z5" s="92"/>
@@ -2033,7 +2019,7 @@
       <c r="AG5" s="92"/>
       <c r="AH5" s="92"/>
     </row>
-    <row r="6" spans="1:60" s="11" customFormat="1" ht="18.75">
+    <row r="6" spans="1:60" s="11" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A6" s="85"/>
       <c r="B6" s="85"/>
       <c r="C6" s="85"/>
@@ -2054,9 +2040,7 @@
       <c r="T6" s="16"/>
       <c r="U6" s="16"/>
       <c r="V6" s="92"/>
-      <c r="W6" s="94" t="s">
-        <v>169</v>
-      </c>
+      <c r="W6" s="94"/>
       <c r="X6" s="92"/>
       <c r="Y6" s="92"/>
       <c r="Z6" s="92"/>
@@ -2069,7 +2053,7 @@
       <c r="AG6" s="92"/>
       <c r="AH6" s="92"/>
     </row>
-    <row r="7" spans="1:60" s="11" customFormat="1" ht="18.75">
+    <row r="7" spans="1:60" s="11" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A7" s="85"/>
       <c r="B7" s="85"/>
       <c r="C7" s="85"/>
@@ -2090,9 +2074,7 @@
       <c r="T7" s="16"/>
       <c r="U7" s="16"/>
       <c r="V7" s="92"/>
-      <c r="W7" s="94" t="s">
-        <v>1</v>
-      </c>
+      <c r="W7" s="94"/>
       <c r="X7" s="92"/>
       <c r="Y7" s="92"/>
       <c r="Z7" s="92"/>
@@ -2105,7 +2087,7 @@
       <c r="AG7" s="92"/>
       <c r="AH7" s="92"/>
     </row>
-    <row r="8" spans="1:60" s="11" customFormat="1" ht="18.75">
+    <row r="8" spans="1:60" s="11" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A8" s="85"/>
       <c r="B8" s="85"/>
       <c r="C8" s="85"/>
@@ -2126,9 +2108,7 @@
       <c r="T8" s="16"/>
       <c r="U8" s="16"/>
       <c r="V8" s="92"/>
-      <c r="W8" s="94" t="s">
-        <v>170</v>
-      </c>
+      <c r="W8" s="94"/>
       <c r="X8" s="92"/>
       <c r="Y8" s="92"/>
       <c r="Z8" s="92"/>
@@ -2141,7 +2121,7 @@
       <c r="AG8" s="92"/>
       <c r="AH8" s="92"/>
     </row>
-    <row r="9" spans="1:60" s="11" customFormat="1">
+    <row r="9" spans="1:60" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A9" s="85"/>
       <c r="B9" s="85"/>
       <c r="C9" s="85"/>
@@ -2175,7 +2155,7 @@
       <c r="AG9" s="92"/>
       <c r="AH9" s="92"/>
     </row>
-    <row r="10" spans="1:60" s="11" customFormat="1" ht="18.75">
+    <row r="10" spans="1:60" s="11" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A10" s="85"/>
       <c r="B10" s="85"/>
       <c r="C10" s="85"/>
@@ -2196,9 +2176,7 @@
       <c r="T10" s="96"/>
       <c r="U10" s="96"/>
       <c r="V10" s="85"/>
-      <c r="W10" s="94" t="s">
-        <v>171</v>
-      </c>
+      <c r="W10" s="94"/>
       <c r="X10" s="85"/>
       <c r="Y10" s="85"/>
       <c r="Z10" s="85"/>
@@ -2211,7 +2189,7 @@
       <c r="AG10" s="85"/>
       <c r="AH10" s="85"/>
     </row>
-    <row r="11" spans="1:60" s="11" customFormat="1" ht="18.75">
+    <row r="11" spans="1:60" s="11" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A11" s="85"/>
       <c r="B11" s="85"/>
       <c r="C11" s="85"/>
@@ -2234,9 +2212,7 @@
       <c r="T11" s="96"/>
       <c r="U11" s="96"/>
       <c r="V11" s="85"/>
-      <c r="W11" s="94" t="s">
-        <v>172</v>
-      </c>
+      <c r="W11" s="94"/>
       <c r="X11" s="85"/>
       <c r="Y11" s="85"/>
       <c r="Z11" s="85"/>
@@ -2249,7 +2225,7 @@
       <c r="AG11" s="85"/>
       <c r="AH11" s="85"/>
     </row>
-    <row r="12" spans="1:60" s="11" customFormat="1">
+    <row r="12" spans="1:60" s="11" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A12" s="85"/>
       <c r="B12" s="85"/>
       <c r="C12" s="85"/>
@@ -2286,36 +2262,36 @@
       <c r="AH12" s="85"/>
       <c r="AI12" s="16"/>
     </row>
-    <row r="13" spans="1:60" s="11" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A13" s="155" t="s">
-        <v>162</v>
-      </c>
-      <c r="B13" s="156"/>
-      <c r="C13" s="156"/>
-      <c r="D13" s="156"/>
-      <c r="E13" s="156"/>
-      <c r="F13" s="156"/>
-      <c r="G13" s="156"/>
-      <c r="H13" s="156"/>
-      <c r="I13" s="156"/>
-      <c r="J13" s="156"/>
-      <c r="K13" s="156"/>
-      <c r="L13" s="156"/>
-      <c r="M13" s="156"/>
-      <c r="N13" s="156"/>
-      <c r="O13" s="156"/>
-      <c r="P13" s="156"/>
-      <c r="Q13" s="156"/>
-      <c r="R13" s="156"/>
-      <c r="S13" s="156"/>
-      <c r="T13" s="156"/>
-      <c r="U13" s="156"/>
-      <c r="V13" s="157"/>
-      <c r="W13" s="157"/>
-      <c r="X13" s="157"/>
-      <c r="Y13" s="157"/>
-      <c r="Z13" s="157"/>
-      <c r="AA13" s="157"/>
+    <row r="13" spans="1:60" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="113" t="s">
+        <v>153</v>
+      </c>
+      <c r="B13" s="114"/>
+      <c r="C13" s="114"/>
+      <c r="D13" s="114"/>
+      <c r="E13" s="114"/>
+      <c r="F13" s="114"/>
+      <c r="G13" s="114"/>
+      <c r="H13" s="114"/>
+      <c r="I13" s="114"/>
+      <c r="J13" s="114"/>
+      <c r="K13" s="114"/>
+      <c r="L13" s="114"/>
+      <c r="M13" s="114"/>
+      <c r="N13" s="114"/>
+      <c r="O13" s="114"/>
+      <c r="P13" s="114"/>
+      <c r="Q13" s="114"/>
+      <c r="R13" s="114"/>
+      <c r="S13" s="114"/>
+      <c r="T13" s="114"/>
+      <c r="U13" s="114"/>
+      <c r="V13" s="115"/>
+      <c r="W13" s="115"/>
+      <c r="X13" s="115"/>
+      <c r="Y13" s="115"/>
+      <c r="Z13" s="115"/>
+      <c r="AA13" s="115"/>
       <c r="AB13" s="97"/>
       <c r="AC13" s="98"/>
       <c r="AD13" s="98"/>
@@ -2324,36 +2300,36 @@
       <c r="AG13" s="98"/>
       <c r="AH13" s="98"/>
     </row>
-    <row r="14" spans="1:60" s="11" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A14" s="155" t="s">
-        <v>159</v>
-      </c>
-      <c r="B14" s="156"/>
-      <c r="C14" s="156"/>
-      <c r="D14" s="156"/>
-      <c r="E14" s="156"/>
-      <c r="F14" s="156"/>
-      <c r="G14" s="156"/>
-      <c r="H14" s="156"/>
-      <c r="I14" s="156"/>
-      <c r="J14" s="156"/>
-      <c r="K14" s="156"/>
-      <c r="L14" s="156"/>
-      <c r="M14" s="156"/>
-      <c r="N14" s="156"/>
-      <c r="O14" s="156"/>
-      <c r="P14" s="156"/>
-      <c r="Q14" s="156"/>
-      <c r="R14" s="156"/>
-      <c r="S14" s="156"/>
-      <c r="T14" s="156"/>
-      <c r="U14" s="156"/>
-      <c r="V14" s="157"/>
-      <c r="W14" s="157"/>
-      <c r="X14" s="157"/>
-      <c r="Y14" s="157"/>
-      <c r="Z14" s="157"/>
-      <c r="AA14" s="157"/>
+    <row r="14" spans="1:60" s="11" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="113" t="s">
+        <v>152</v>
+      </c>
+      <c r="B14" s="114"/>
+      <c r="C14" s="114"/>
+      <c r="D14" s="114"/>
+      <c r="E14" s="114"/>
+      <c r="F14" s="114"/>
+      <c r="G14" s="114"/>
+      <c r="H14" s="114"/>
+      <c r="I14" s="114"/>
+      <c r="J14" s="114"/>
+      <c r="K14" s="114"/>
+      <c r="L14" s="114"/>
+      <c r="M14" s="114"/>
+      <c r="N14" s="114"/>
+      <c r="O14" s="114"/>
+      <c r="P14" s="114"/>
+      <c r="Q14" s="114"/>
+      <c r="R14" s="114"/>
+      <c r="S14" s="114"/>
+      <c r="T14" s="114"/>
+      <c r="U14" s="114"/>
+      <c r="V14" s="115"/>
+      <c r="W14" s="115"/>
+      <c r="X14" s="115"/>
+      <c r="Y14" s="115"/>
+      <c r="Z14" s="115"/>
+      <c r="AA14" s="115"/>
       <c r="AB14" s="97"/>
       <c r="AC14" s="99"/>
       <c r="AD14" s="99"/>
@@ -2362,36 +2338,36 @@
       <c r="AG14" s="99"/>
       <c r="AH14" s="99"/>
     </row>
-    <row r="15" spans="1:60" s="11" customFormat="1" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A15" s="158" t="s">
-        <v>2</v>
-      </c>
-      <c r="B15" s="159"/>
-      <c r="C15" s="159"/>
-      <c r="D15" s="159"/>
-      <c r="E15" s="159"/>
-      <c r="F15" s="159"/>
-      <c r="G15" s="159"/>
-      <c r="H15" s="159"/>
-      <c r="I15" s="159"/>
-      <c r="J15" s="159"/>
-      <c r="K15" s="159"/>
-      <c r="L15" s="159"/>
-      <c r="M15" s="159"/>
-      <c r="N15" s="159"/>
-      <c r="O15" s="159"/>
-      <c r="P15" s="159"/>
-      <c r="Q15" s="159"/>
-      <c r="R15" s="159"/>
-      <c r="S15" s="159"/>
-      <c r="T15" s="159"/>
-      <c r="U15" s="159"/>
-      <c r="V15" s="157"/>
-      <c r="W15" s="157"/>
-      <c r="X15" s="157"/>
-      <c r="Y15" s="157"/>
-      <c r="Z15" s="157"/>
-      <c r="AA15" s="157"/>
+    <row r="15" spans="1:60" s="11" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="116" t="s">
+        <v>0</v>
+      </c>
+      <c r="B15" s="117"/>
+      <c r="C15" s="117"/>
+      <c r="D15" s="117"/>
+      <c r="E15" s="117"/>
+      <c r="F15" s="117"/>
+      <c r="G15" s="117"/>
+      <c r="H15" s="117"/>
+      <c r="I15" s="117"/>
+      <c r="J15" s="117"/>
+      <c r="K15" s="117"/>
+      <c r="L15" s="117"/>
+      <c r="M15" s="117"/>
+      <c r="N15" s="117"/>
+      <c r="O15" s="117"/>
+      <c r="P15" s="117"/>
+      <c r="Q15" s="117"/>
+      <c r="R15" s="117"/>
+      <c r="S15" s="117"/>
+      <c r="T15" s="117"/>
+      <c r="U15" s="117"/>
+      <c r="V15" s="115"/>
+      <c r="W15" s="115"/>
+      <c r="X15" s="115"/>
+      <c r="Y15" s="115"/>
+      <c r="Z15" s="115"/>
+      <c r="AA15" s="115"/>
       <c r="AB15" s="97"/>
       <c r="AC15" s="100"/>
       <c r="AD15" s="100"/>
@@ -2400,32 +2376,32 @@
       <c r="AG15" s="100"/>
       <c r="AH15" s="100"/>
     </row>
-    <row r="16" spans="1:60" s="4" customFormat="1" ht="15.75" customHeight="1">
-      <c r="A16" s="136" t="s">
+    <row r="16" spans="1:60" s="4" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="119" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" s="119" t="s">
+        <v>2</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="B16" s="136" t="s">
+      <c r="D16" s="2"/>
+      <c r="E16" s="119" t="s">
         <v>4</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="F16" s="119"/>
+      <c r="G16" s="119"/>
+      <c r="H16" s="119"/>
+      <c r="I16" s="119"/>
+      <c r="J16" s="119"/>
+      <c r="K16" s="118"/>
+      <c r="L16" s="118" t="s">
+        <v>50</v>
+      </c>
+      <c r="M16" s="118"/>
+      <c r="N16" s="19" t="s">
         <v>5</v>
-      </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="136" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" s="136"/>
-      <c r="G16" s="136"/>
-      <c r="H16" s="136"/>
-      <c r="I16" s="136"/>
-      <c r="J16" s="136"/>
-      <c r="K16" s="135"/>
-      <c r="L16" s="135" t="s">
-        <v>57</v>
-      </c>
-      <c r="M16" s="135"/>
-      <c r="N16" s="19" t="s">
-        <v>7</v>
       </c>
       <c r="O16" s="19"/>
       <c r="P16" s="19"/>
@@ -2435,342 +2411,342 @@
       <c r="T16" s="19"/>
       <c r="U16" s="19"/>
       <c r="V16" s="19"/>
-      <c r="W16" s="137" t="s">
-        <v>26</v>
-      </c>
-      <c r="X16" s="134" t="s">
-        <v>27</v>
-      </c>
-      <c r="Y16" s="137" t="s">
-        <v>28</v>
-      </c>
-      <c r="Z16" s="134" t="s">
-        <v>29</v>
-      </c>
-      <c r="AA16" s="134" t="s">
-        <v>30</v>
-      </c>
-      <c r="AB16" s="113" t="s">
-        <v>164</v>
+      <c r="W16" s="139" t="s">
+        <v>19</v>
+      </c>
+      <c r="X16" s="138" t="s">
+        <v>20</v>
+      </c>
+      <c r="Y16" s="139" t="s">
+        <v>21</v>
+      </c>
+      <c r="Z16" s="138" t="s">
+        <v>22</v>
+      </c>
+      <c r="AA16" s="138" t="s">
+        <v>23</v>
+      </c>
+      <c r="AB16" s="143" t="s">
+        <v>155</v>
       </c>
       <c r="AC16" s="31"/>
-      <c r="AD16" s="126" t="s">
+      <c r="AD16" s="156" t="s">
+        <v>87</v>
+      </c>
+      <c r="AE16" s="124" t="s">
+        <v>50</v>
+      </c>
+      <c r="AF16" s="124"/>
+      <c r="AG16" s="124" t="s">
+        <v>88</v>
+      </c>
+      <c r="AH16" s="157"/>
+      <c r="AI16" s="158" t="s">
+        <v>89</v>
+      </c>
+      <c r="AJ16" s="158" t="s">
+        <v>90</v>
+      </c>
+      <c r="AK16" s="122" t="s">
+        <v>50</v>
+      </c>
+      <c r="AL16" s="122"/>
+      <c r="AM16" s="122" t="s">
+        <v>88</v>
+      </c>
+      <c r="AN16" s="123"/>
+      <c r="AO16" s="45"/>
+      <c r="AP16" s="145" t="s">
+        <v>117</v>
+      </c>
+      <c r="AQ16" s="146"/>
+      <c r="AR16" s="146"/>
+      <c r="AS16" s="146"/>
+      <c r="AT16" s="146"/>
+      <c r="AU16" s="146"/>
+      <c r="AV16" s="147"/>
+      <c r="AW16" s="145" t="s">
+        <v>123</v>
+      </c>
+      <c r="AX16" s="146"/>
+      <c r="AY16" s="146"/>
+      <c r="AZ16" s="146"/>
+      <c r="BA16" s="146"/>
+      <c r="BB16" s="146"/>
+      <c r="BC16" s="147"/>
+    </row>
+    <row r="17" spans="1:66" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="119"/>
+      <c r="B17" s="119"/>
+      <c r="C17" s="119" t="s">
+        <v>6</v>
+      </c>
+      <c r="D17" s="119" t="s">
+        <v>7</v>
+      </c>
+      <c r="E17" s="119" t="s">
+        <v>47</v>
+      </c>
+      <c r="F17" s="119" t="s">
+        <v>8</v>
+      </c>
+      <c r="G17" s="119"/>
+      <c r="H17" s="118"/>
+      <c r="I17" s="119" t="s">
+        <v>9</v>
+      </c>
+      <c r="J17" s="119"/>
+      <c r="K17" s="118"/>
+      <c r="L17" s="120" t="s">
+        <v>8</v>
+      </c>
+      <c r="M17" s="121" t="s">
+        <v>9</v>
+      </c>
+      <c r="N17" s="130" t="s">
+        <v>8</v>
+      </c>
+      <c r="O17" s="130"/>
+      <c r="P17" s="130" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q17" s="118"/>
+      <c r="R17" s="130" t="s">
+        <v>10</v>
+      </c>
+      <c r="S17" s="131" t="s">
+        <v>11</v>
+      </c>
+      <c r="T17" s="142" t="s">
+        <v>12</v>
+      </c>
+      <c r="U17" s="136" t="s">
+        <v>71</v>
+      </c>
+      <c r="V17" s="136" t="s">
+        <v>72</v>
+      </c>
+      <c r="W17" s="139"/>
+      <c r="X17" s="138"/>
+      <c r="Y17" s="139"/>
+      <c r="Z17" s="138"/>
+      <c r="AA17" s="138"/>
+      <c r="AB17" s="143"/>
+      <c r="AC17" s="32"/>
+      <c r="AD17" s="125"/>
+      <c r="AE17" s="124" t="s">
+        <v>91</v>
+      </c>
+      <c r="AF17" s="124" t="s">
+        <v>92</v>
+      </c>
+      <c r="AG17" s="124" t="s">
+        <v>91</v>
+      </c>
+      <c r="AH17" s="124" t="s">
+        <v>92</v>
+      </c>
+      <c r="AI17" s="159"/>
+      <c r="AJ17" s="159"/>
+      <c r="AK17" s="123" t="s">
+        <v>93</v>
+      </c>
+      <c r="AL17" s="123" t="s">
         <v>94</v>
       </c>
-      <c r="AE16" s="128" t="s">
-        <v>57</v>
-      </c>
-      <c r="AF16" s="128"/>
-      <c r="AG16" s="128" t="s">
-        <v>95</v>
-      </c>
-      <c r="AH16" s="129"/>
-      <c r="AI16" s="130" t="s">
-        <v>96</v>
-      </c>
-      <c r="AJ16" s="130" t="s">
-        <v>97</v>
-      </c>
-      <c r="AK16" s="153" t="s">
-        <v>57</v>
-      </c>
-      <c r="AL16" s="153"/>
-      <c r="AM16" s="153" t="s">
-        <v>95</v>
-      </c>
-      <c r="AN16" s="154"/>
-      <c r="AO16" s="45"/>
-      <c r="AP16" s="115" t="s">
-        <v>124</v>
-      </c>
-      <c r="AQ16" s="116"/>
-      <c r="AR16" s="116"/>
-      <c r="AS16" s="116"/>
-      <c r="AT16" s="116"/>
-      <c r="AU16" s="116"/>
-      <c r="AV16" s="117"/>
-      <c r="AW16" s="115" t="s">
-        <v>130</v>
-      </c>
-      <c r="AX16" s="116"/>
-      <c r="AY16" s="116"/>
-      <c r="AZ16" s="116"/>
-      <c r="BA16" s="116"/>
-      <c r="BB16" s="116"/>
-      <c r="BC16" s="117"/>
+      <c r="AM17" s="123" t="s">
+        <v>93</v>
+      </c>
+      <c r="AN17" s="123" t="s">
+        <v>94</v>
+      </c>
+      <c r="AO17" s="45"/>
+      <c r="AP17" s="148" t="s">
+        <v>118</v>
+      </c>
+      <c r="AQ17" s="150" t="s">
+        <v>119</v>
+      </c>
+      <c r="AR17" s="151"/>
+      <c r="AS17" s="152" t="s">
+        <v>120</v>
+      </c>
+      <c r="AT17" s="153"/>
+      <c r="AU17" s="154" t="s">
+        <v>77</v>
+      </c>
+      <c r="AV17" s="155"/>
+      <c r="AW17" s="148" t="s">
+        <v>118</v>
+      </c>
+      <c r="AX17" s="150" t="s">
+        <v>119</v>
+      </c>
+      <c r="AY17" s="151"/>
+      <c r="AZ17" s="152" t="s">
+        <v>120</v>
+      </c>
+      <c r="BA17" s="153"/>
+      <c r="BB17" s="154" t="s">
+        <v>77</v>
+      </c>
+      <c r="BC17" s="155"/>
     </row>
-    <row r="17" spans="1:66" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A17" s="136"/>
-      <c r="B17" s="136"/>
-      <c r="C17" s="136" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="136" t="s">
-        <v>9</v>
-      </c>
-      <c r="E17" s="136" t="s">
-        <v>54</v>
-      </c>
-      <c r="F17" s="136" t="s">
-        <v>10</v>
-      </c>
-      <c r="G17" s="136"/>
-      <c r="H17" s="135"/>
-      <c r="I17" s="136" t="s">
-        <v>11</v>
-      </c>
-      <c r="J17" s="136"/>
-      <c r="K17" s="135"/>
-      <c r="L17" s="143" t="s">
-        <v>10</v>
-      </c>
-      <c r="M17" s="141" t="s">
-        <v>11</v>
-      </c>
-      <c r="N17" s="149" t="s">
-        <v>10</v>
-      </c>
-      <c r="O17" s="149"/>
-      <c r="P17" s="149" t="s">
-        <v>11</v>
-      </c>
-      <c r="Q17" s="135"/>
-      <c r="R17" s="149" t="s">
-        <v>12</v>
-      </c>
-      <c r="S17" s="150" t="s">
-        <v>13</v>
-      </c>
-      <c r="T17" s="140" t="s">
-        <v>14</v>
-      </c>
-      <c r="U17" s="132" t="s">
-        <v>78</v>
-      </c>
-      <c r="V17" s="132" t="s">
-        <v>79</v>
-      </c>
-      <c r="W17" s="137"/>
-      <c r="X17" s="134"/>
-      <c r="Y17" s="137"/>
-      <c r="Z17" s="134"/>
-      <c r="AA17" s="134"/>
-      <c r="AB17" s="113"/>
-      <c r="AC17" s="32"/>
-      <c r="AD17" s="127"/>
-      <c r="AE17" s="128" t="s">
-        <v>98</v>
-      </c>
-      <c r="AF17" s="128" t="s">
-        <v>99</v>
-      </c>
-      <c r="AG17" s="128" t="s">
-        <v>98</v>
-      </c>
-      <c r="AH17" s="128" t="s">
-        <v>99</v>
-      </c>
-      <c r="AI17" s="131"/>
-      <c r="AJ17" s="131"/>
-      <c r="AK17" s="154" t="s">
-        <v>100</v>
-      </c>
-      <c r="AL17" s="154" t="s">
-        <v>101</v>
-      </c>
-      <c r="AM17" s="154" t="s">
-        <v>100</v>
-      </c>
-      <c r="AN17" s="154" t="s">
-        <v>101</v>
-      </c>
-      <c r="AO17" s="45"/>
-      <c r="AP17" s="118" t="s">
-        <v>125</v>
-      </c>
-      <c r="AQ17" s="120" t="s">
-        <v>126</v>
-      </c>
-      <c r="AR17" s="121"/>
-      <c r="AS17" s="122" t="s">
-        <v>127</v>
-      </c>
-      <c r="AT17" s="123"/>
-      <c r="AU17" s="124" t="s">
-        <v>84</v>
-      </c>
-      <c r="AV17" s="125"/>
-      <c r="AW17" s="118" t="s">
-        <v>125</v>
-      </c>
-      <c r="AX17" s="120" t="s">
-        <v>126</v>
-      </c>
-      <c r="AY17" s="121"/>
-      <c r="AZ17" s="122" t="s">
-        <v>127</v>
-      </c>
-      <c r="BA17" s="123"/>
-      <c r="BB17" s="124" t="s">
-        <v>84</v>
-      </c>
-      <c r="BC17" s="125"/>
+    <row r="18" spans="1:66" s="4" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A18" s="119"/>
+      <c r="B18" s="119"/>
+      <c r="C18" s="119"/>
+      <c r="D18" s="119"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="140" t="s">
+        <v>65</v>
+      </c>
+      <c r="G18" s="141"/>
+      <c r="H18" s="134" t="s">
+        <v>66</v>
+      </c>
+      <c r="I18" s="132" t="s">
+        <v>65</v>
+      </c>
+      <c r="J18" s="133"/>
+      <c r="K18" s="135" t="s">
+        <v>66</v>
+      </c>
+      <c r="L18" s="120"/>
+      <c r="M18" s="121"/>
+      <c r="N18" s="134" t="s">
+        <v>65</v>
+      </c>
+      <c r="O18" s="134" t="s">
+        <v>66</v>
+      </c>
+      <c r="P18" s="135" t="s">
+        <v>65</v>
+      </c>
+      <c r="Q18" s="135" t="s">
+        <v>66</v>
+      </c>
+      <c r="R18" s="130"/>
+      <c r="S18" s="131"/>
+      <c r="T18" s="142"/>
+      <c r="U18" s="136"/>
+      <c r="V18" s="136"/>
+      <c r="W18" s="139"/>
+      <c r="X18" s="138"/>
+      <c r="Y18" s="139"/>
+      <c r="Z18" s="138"/>
+      <c r="AA18" s="138"/>
+      <c r="AB18" s="143"/>
+      <c r="AC18" s="33"/>
+      <c r="AD18" s="125"/>
+      <c r="AE18" s="125"/>
+      <c r="AF18" s="125"/>
+      <c r="AG18" s="125"/>
+      <c r="AH18" s="125"/>
+      <c r="AI18" s="159"/>
+      <c r="AJ18" s="159"/>
+      <c r="AK18" s="123"/>
+      <c r="AL18" s="123"/>
+      <c r="AM18" s="123"/>
+      <c r="AN18" s="123"/>
+      <c r="AO18" s="45"/>
+      <c r="AP18" s="149"/>
+      <c r="AQ18" s="52" t="s">
+        <v>121</v>
+      </c>
+      <c r="AR18" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="AS18" s="54" t="s">
+        <v>121</v>
+      </c>
+      <c r="AT18" s="55" t="s">
+        <v>122</v>
+      </c>
+      <c r="AU18" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="AV18" s="57" t="s">
+        <v>122</v>
+      </c>
+      <c r="AW18" s="149"/>
+      <c r="AX18" s="52" t="s">
+        <v>121</v>
+      </c>
+      <c r="AY18" s="53" t="s">
+        <v>122</v>
+      </c>
+      <c r="AZ18" s="54" t="s">
+        <v>121</v>
+      </c>
+      <c r="BA18" s="55" t="s">
+        <v>122</v>
+      </c>
+      <c r="BB18" s="56" t="s">
+        <v>121</v>
+      </c>
+      <c r="BC18" s="57" t="s">
+        <v>122</v>
+      </c>
     </row>
-    <row r="18" spans="1:66" s="4" customFormat="1" ht="15" customHeight="1">
-      <c r="A18" s="136"/>
-      <c r="B18" s="136"/>
-      <c r="C18" s="136"/>
-      <c r="D18" s="136"/>
-      <c r="E18" s="135"/>
-      <c r="F18" s="138" t="s">
-        <v>72</v>
-      </c>
-      <c r="G18" s="139"/>
-      <c r="H18" s="142" t="s">
-        <v>73</v>
-      </c>
-      <c r="I18" s="151" t="s">
-        <v>72</v>
-      </c>
-      <c r="J18" s="152"/>
-      <c r="K18" s="144" t="s">
-        <v>73</v>
-      </c>
-      <c r="L18" s="143"/>
-      <c r="M18" s="141"/>
-      <c r="N18" s="142" t="s">
-        <v>72</v>
-      </c>
-      <c r="O18" s="142" t="s">
-        <v>73</v>
-      </c>
-      <c r="P18" s="144" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q18" s="144" t="s">
-        <v>73</v>
-      </c>
-      <c r="R18" s="149"/>
-      <c r="S18" s="150"/>
-      <c r="T18" s="140"/>
-      <c r="U18" s="132"/>
-      <c r="V18" s="132"/>
-      <c r="W18" s="137"/>
-      <c r="X18" s="134"/>
-      <c r="Y18" s="137"/>
-      <c r="Z18" s="134"/>
-      <c r="AA18" s="134"/>
-      <c r="AB18" s="113"/>
-      <c r="AC18" s="33"/>
-      <c r="AD18" s="127"/>
-      <c r="AE18" s="127"/>
-      <c r="AF18" s="127"/>
-      <c r="AG18" s="127"/>
-      <c r="AH18" s="127"/>
-      <c r="AI18" s="131"/>
-      <c r="AJ18" s="131"/>
-      <c r="AK18" s="154"/>
-      <c r="AL18" s="154"/>
-      <c r="AM18" s="154"/>
-      <c r="AN18" s="154"/>
-      <c r="AO18" s="45"/>
-      <c r="AP18" s="119"/>
-      <c r="AQ18" s="52" t="s">
-        <v>128</v>
-      </c>
-      <c r="AR18" s="53" t="s">
-        <v>129</v>
-      </c>
-      <c r="AS18" s="54" t="s">
-        <v>128</v>
-      </c>
-      <c r="AT18" s="55" t="s">
-        <v>129</v>
-      </c>
-      <c r="AU18" s="56" t="s">
-        <v>128</v>
-      </c>
-      <c r="AV18" s="57" t="s">
-        <v>129</v>
-      </c>
-      <c r="AW18" s="119"/>
-      <c r="AX18" s="52" t="s">
-        <v>128</v>
-      </c>
-      <c r="AY18" s="53" t="s">
-        <v>129</v>
-      </c>
-      <c r="AZ18" s="54" t="s">
-        <v>128</v>
-      </c>
-      <c r="BA18" s="55" t="s">
-        <v>129</v>
-      </c>
-      <c r="BB18" s="56" t="s">
-        <v>128</v>
-      </c>
-      <c r="BC18" s="57" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="19" spans="1:66" s="4" customFormat="1" ht="79.5" customHeight="1">
-      <c r="A19" s="135"/>
-      <c r="B19" s="135"/>
-      <c r="C19" s="135"/>
-      <c r="D19" s="135"/>
-      <c r="E19" s="135"/>
+    <row r="19" spans="1:66" s="4" customFormat="1" ht="79.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A19" s="118"/>
+      <c r="B19" s="118"/>
+      <c r="C19" s="118"/>
+      <c r="D19" s="118"/>
+      <c r="E19" s="118"/>
       <c r="F19" s="28" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="G19" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="H19" s="143"/>
+        <v>77</v>
+      </c>
+      <c r="H19" s="120"/>
       <c r="I19" s="29" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="J19" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="K19" s="141"/>
-      <c r="L19" s="143"/>
-      <c r="M19" s="141"/>
-      <c r="N19" s="143"/>
-      <c r="O19" s="143"/>
-      <c r="P19" s="141"/>
-      <c r="Q19" s="141"/>
-      <c r="R19" s="135"/>
-      <c r="S19" s="143"/>
-      <c r="T19" s="141"/>
-      <c r="U19" s="133"/>
-      <c r="V19" s="133"/>
-      <c r="W19" s="135"/>
-      <c r="X19" s="135"/>
-      <c r="Y19" s="135"/>
-      <c r="Z19" s="135"/>
-      <c r="AA19" s="135"/>
-      <c r="AB19" s="114"/>
+        <v>77</v>
+      </c>
+      <c r="K19" s="121"/>
+      <c r="L19" s="120"/>
+      <c r="M19" s="121"/>
+      <c r="N19" s="120"/>
+      <c r="O19" s="120"/>
+      <c r="P19" s="121"/>
+      <c r="Q19" s="121"/>
+      <c r="R19" s="118"/>
+      <c r="S19" s="120"/>
+      <c r="T19" s="121"/>
+      <c r="U19" s="137"/>
+      <c r="V19" s="137"/>
+      <c r="W19" s="118"/>
+      <c r="X19" s="118"/>
+      <c r="Y19" s="118"/>
+      <c r="Z19" s="118"/>
+      <c r="AA19" s="118"/>
+      <c r="AB19" s="144"/>
       <c r="AC19" s="33"/>
-      <c r="AD19" s="127"/>
-      <c r="AE19" s="127"/>
-      <c r="AF19" s="127"/>
-      <c r="AG19" s="127"/>
-      <c r="AH19" s="127"/>
-      <c r="AI19" s="131"/>
-      <c r="AJ19" s="131"/>
-      <c r="AK19" s="154"/>
-      <c r="AL19" s="154"/>
-      <c r="AM19" s="154"/>
-      <c r="AN19" s="154"/>
+      <c r="AD19" s="125"/>
+      <c r="AE19" s="125"/>
+      <c r="AF19" s="125"/>
+      <c r="AG19" s="125"/>
+      <c r="AH19" s="125"/>
+      <c r="AI19" s="159"/>
+      <c r="AJ19" s="159"/>
+      <c r="AK19" s="123"/>
+      <c r="AL19" s="123"/>
+      <c r="AM19" s="123"/>
+      <c r="AN19" s="123"/>
       <c r="AO19" s="45"/>
-      <c r="AP19" s="119"/>
+      <c r="AP19" s="149"/>
       <c r="AQ19" s="52"/>
       <c r="AR19" s="53"/>
       <c r="AS19" s="54"/>
       <c r="AT19" s="55"/>
       <c r="AU19" s="56"/>
       <c r="AV19" s="57"/>
-      <c r="AW19" s="119"/>
+      <c r="AW19" s="149"/>
       <c r="AX19" s="52"/>
       <c r="AY19" s="53"/>
       <c r="AZ19" s="54"/>
@@ -2778,7 +2754,7 @@
       <c r="BB19" s="56"/>
       <c r="BC19" s="57"/>
     </row>
-    <row r="20" spans="1:66">
+    <row r="20" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A20" s="6">
         <v>1</v>
       </c>
@@ -2942,182 +2918,182 @@
       </c>
       <c r="BE20" s="13"/>
       <c r="BI20" s="10" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="BJ20" s="10" t="s">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="BL20" s="11"/>
       <c r="BM20" s="11"/>
       <c r="BN20" s="11"/>
     </row>
-    <row r="21" spans="1:66">
+    <row r="21" spans="1:66" x14ac:dyDescent="0.25">
       <c r="A21" s="3"/>
       <c r="B21" s="8" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="C21" s="5"/>
       <c r="D21" s="5"/>
       <c r="E21" s="9" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F21" s="23" t="s">
+        <v>78</v>
+      </c>
+      <c r="G21" s="23" t="s">
+        <v>80</v>
+      </c>
+      <c r="H21" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="I21" s="22" t="s">
+        <v>83</v>
+      </c>
+      <c r="J21" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="G21" s="23" t="s">
-        <v>87</v>
-      </c>
-      <c r="H21" s="20" t="s">
+      <c r="K21" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="L21" s="23" t="s">
+        <v>67</v>
+      </c>
+      <c r="M21" s="22" t="s">
+        <v>68</v>
+      </c>
+      <c r="N21" s="20" t="s">
+        <v>51</v>
+      </c>
+      <c r="O21" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="P21" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q21" s="21" t="s">
+        <v>53</v>
+      </c>
+      <c r="R21" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="S21" s="20" t="s">
+        <v>56</v>
+      </c>
+      <c r="T21" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="I21" s="22" t="s">
-        <v>90</v>
-      </c>
-      <c r="J21" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="K21" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="L21" s="23" t="s">
-        <v>74</v>
-      </c>
-      <c r="M21" s="22" t="s">
+      <c r="U21" s="27" t="s">
+        <v>73</v>
+      </c>
+      <c r="V21" s="27" t="s">
         <v>75</v>
       </c>
-      <c r="N21" s="20" t="s">
-        <v>58</v>
-      </c>
-      <c r="O21" s="20" t="s">
-        <v>59</v>
-      </c>
-      <c r="P21" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q21" s="21" t="s">
-        <v>60</v>
-      </c>
-      <c r="R21" s="9" t="s">
+      <c r="W21" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="X21" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="S21" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="T21" s="21" t="s">
-        <v>62</v>
-      </c>
-      <c r="U21" s="27" t="s">
-        <v>80</v>
-      </c>
-      <c r="V21" s="27" t="s">
-        <v>82</v>
-      </c>
-      <c r="W21" s="9" t="s">
+      <c r="Y21" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="X21" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="Y21" s="9" t="s">
-        <v>32</v>
-      </c>
       <c r="Z21" s="9" t="s">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="AA21" s="79" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="AB21" s="83" t="s">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="AC21" s="35"/>
       <c r="AD21" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="AE21" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="AF21" s="38" t="s">
+        <v>97</v>
+      </c>
+      <c r="AG21" s="38" t="s">
+        <v>98</v>
+      </c>
+      <c r="AH21" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="AI21" s="39" t="s">
+        <v>100</v>
+      </c>
+      <c r="AJ21" s="39" t="s">
+        <v>101</v>
+      </c>
+      <c r="AK21" s="40" t="s">
         <v>102</v>
       </c>
-      <c r="AE21" s="38" t="s">
+      <c r="AL21" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="AF21" s="38" t="s">
+      <c r="AM21" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="AG21" s="38" t="s">
+      <c r="AN21" s="40" t="s">
         <v>105</v>
-      </c>
-      <c r="AH21" s="38" t="s">
-        <v>106</v>
-      </c>
-      <c r="AI21" s="39" t="s">
-        <v>107</v>
-      </c>
-      <c r="AJ21" s="39" t="s">
-        <v>108</v>
-      </c>
-      <c r="AK21" s="40" t="s">
-        <v>109</v>
-      </c>
-      <c r="AL21" s="40" t="s">
-        <v>110</v>
-      </c>
-      <c r="AM21" s="40" t="s">
-        <v>111</v>
-      </c>
-      <c r="AN21" s="40" t="s">
-        <v>112</v>
       </c>
       <c r="AO21" s="46"/>
       <c r="AP21" s="58" t="s">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="AQ21" s="59" t="s">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="AR21" s="64" t="s">
+        <v>132</v>
+      </c>
+      <c r="AS21" s="60" t="s">
+        <v>128</v>
+      </c>
+      <c r="AT21" s="66" t="s">
+        <v>134</v>
+      </c>
+      <c r="AU21" s="61" t="s">
+        <v>130</v>
+      </c>
+      <c r="AV21" s="67" t="s">
+        <v>136</v>
+      </c>
+      <c r="AW21" s="58" t="s">
+        <v>138</v>
+      </c>
+      <c r="AX21" s="59" t="s">
         <v>139</v>
       </c>
-      <c r="AS21" s="60" t="s">
-        <v>135</v>
-      </c>
-      <c r="AT21" s="66" t="s">
+      <c r="AY21" s="64" t="s">
+        <v>140</v>
+      </c>
+      <c r="AZ21" s="60" t="s">
         <v>141</v>
       </c>
-      <c r="AU21" s="61" t="s">
-        <v>137</v>
-      </c>
-      <c r="AV21" s="67" t="s">
+      <c r="BA21" s="66" t="s">
+        <v>142</v>
+      </c>
+      <c r="BB21" s="61" t="s">
         <v>143</v>
       </c>
-      <c r="AW21" s="58" t="s">
-        <v>145</v>
-      </c>
-      <c r="AX21" s="59" t="s">
-        <v>146</v>
-      </c>
-      <c r="AY21" s="64" t="s">
-        <v>147</v>
-      </c>
-      <c r="AZ21" s="60" t="s">
-        <v>148</v>
-      </c>
-      <c r="BA21" s="66" t="s">
-        <v>149</v>
-      </c>
-      <c r="BB21" s="61" t="s">
-        <v>150</v>
-      </c>
       <c r="BC21" s="67" t="s">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="BE21" s="14" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="BF21" s="14" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="BG21" s="14">
         <v>1</v>
       </c>
       <c r="BH21" s="12" t="s">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="BI21" s="15"/>
       <c r="BJ21" s="15"/>
@@ -3126,363 +3102,363 @@
       <c r="BM21" s="16"/>
       <c r="BN21" s="16"/>
     </row>
-    <row r="22" spans="1:66">
-      <c r="A22" s="145" t="s">
-        <v>77</v>
-      </c>
-      <c r="B22" s="146"/>
+    <row r="22" spans="1:66" x14ac:dyDescent="0.25">
+      <c r="A22" s="126" t="s">
+        <v>70</v>
+      </c>
+      <c r="B22" s="127"/>
       <c r="C22" s="24"/>
       <c r="D22" s="24"/>
       <c r="E22" s="24" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F22" s="24" t="s">
+        <v>79</v>
+      </c>
+      <c r="G22" s="24" t="s">
+        <v>81</v>
+      </c>
+      <c r="H22" s="24" t="s">
+        <v>57</v>
+      </c>
+      <c r="I22" s="24" t="s">
+        <v>84</v>
+      </c>
+      <c r="J22" s="24" t="s">
         <v>86</v>
       </c>
-      <c r="G22" s="24" t="s">
-        <v>88</v>
-      </c>
-      <c r="H22" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="I22" s="24" t="s">
-        <v>91</v>
-      </c>
-      <c r="J22" s="24" t="s">
-        <v>93</v>
-      </c>
       <c r="K22" s="24" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="L22" s="24"/>
       <c r="M22" s="24"/>
       <c r="N22" s="24" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="O22" s="24" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="P22" s="24" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="Q22" s="24" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="R22" s="24" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="S22" s="24" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="T22" s="24" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="U22" s="24" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="V22" s="24" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="W22" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="X22" s="24" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y22" s="24" t="s">
         <v>25</v>
       </c>
-      <c r="X22" s="24" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y22" s="24" t="s">
+      <c r="Z22" s="24" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA22" s="80" t="s">
+        <v>154</v>
+      </c>
+      <c r="AB22" s="84" t="s">
         <v>32</v>
-      </c>
-      <c r="Z22" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA22" s="80" t="s">
-        <v>163</v>
-      </c>
-      <c r="AB22" s="84" t="s">
-        <v>39</v>
       </c>
       <c r="AC22" s="36"/>
       <c r="AD22" s="42" t="s">
+        <v>106</v>
+      </c>
+      <c r="AE22" s="42" t="s">
+        <v>107</v>
+      </c>
+      <c r="AF22" s="42" t="s">
+        <v>108</v>
+      </c>
+      <c r="AG22" s="42" t="s">
+        <v>109</v>
+      </c>
+      <c r="AH22" s="42" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI22" s="42" t="s">
+        <v>111</v>
+      </c>
+      <c r="AJ22" s="42" t="s">
+        <v>112</v>
+      </c>
+      <c r="AK22" s="42" t="s">
         <v>113</v>
       </c>
-      <c r="AE22" s="42" t="s">
+      <c r="AL22" s="42" t="s">
         <v>114</v>
       </c>
-      <c r="AF22" s="42" t="s">
+      <c r="AM22" s="42" t="s">
         <v>115</v>
       </c>
-      <c r="AG22" s="42" t="s">
+      <c r="AN22" s="42" t="s">
         <v>116</v>
-      </c>
-      <c r="AH22" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="AI22" s="42" t="s">
-        <v>118</v>
-      </c>
-      <c r="AJ22" s="42" t="s">
-        <v>119</v>
-      </c>
-      <c r="AK22" s="42" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL22" s="42" t="s">
-        <v>121</v>
-      </c>
-      <c r="AM22" s="42" t="s">
-        <v>122</v>
-      </c>
-      <c r="AN22" s="42" t="s">
-        <v>123</v>
       </c>
       <c r="AO22" s="47"/>
       <c r="AP22" s="62" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="AQ22" s="63" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="AR22" s="65" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="AS22" s="63" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="AT22" s="65" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AU22" s="63" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="AV22" s="68" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="AW22" s="62" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="AX22" s="63" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="AY22" s="65" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="AZ22" s="63" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="BA22" s="65" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="BB22" s="63" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="BC22" s="68" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="BE22" s="17" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="BF22" s="25" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="BG22" s="17">
         <v>1</v>
       </c>
       <c r="BH22" s="17" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="BI22" s="17" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="BJ22" s="25" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="BK22" s="12"/>
       <c r="BL22" s="16"/>
       <c r="BM22" s="16"/>
       <c r="BN22" s="16"/>
     </row>
-    <row r="23" spans="1:66" ht="15.75" thickBot="1">
-      <c r="A23" s="147" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="148"/>
+    <row r="23" spans="1:66" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="128" t="s">
+        <v>14</v>
+      </c>
+      <c r="B23" s="129"/>
       <c r="C23" s="26"/>
       <c r="D23" s="26"/>
       <c r="E23" s="26" t="s">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="F23" s="26" t="s">
+        <v>79</v>
+      </c>
+      <c r="G23" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="H23" s="26" t="s">
+        <v>57</v>
+      </c>
+      <c r="I23" s="26" t="s">
+        <v>84</v>
+      </c>
+      <c r="J23" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="G23" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="H23" s="26" t="s">
-        <v>64</v>
-      </c>
-      <c r="I23" s="26" t="s">
-        <v>91</v>
-      </c>
-      <c r="J23" s="26" t="s">
-        <v>93</v>
-      </c>
       <c r="K23" s="26" t="s">
-        <v>65</v>
+        <v>58</v>
       </c>
       <c r="L23" s="26"/>
       <c r="M23" s="26"/>
       <c r="N23" s="26" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="O23" s="26" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="P23" s="26" t="s">
-        <v>68</v>
+        <v>61</v>
       </c>
       <c r="Q23" s="26" t="s">
-        <v>69</v>
+        <v>62</v>
       </c>
       <c r="R23" s="26" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="S23" s="26" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="T23" s="26" t="s">
-        <v>71</v>
+        <v>64</v>
       </c>
       <c r="U23" s="26" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="V23" s="26" t="s">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="W23" s="26" t="s">
+        <v>18</v>
+      </c>
+      <c r="X23" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="Y23" s="26" t="s">
         <v>25</v>
       </c>
-      <c r="X23" s="26" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y23" s="26" t="s">
+      <c r="Z23" s="26" t="s">
+        <v>31</v>
+      </c>
+      <c r="AA23" s="81" t="s">
+        <v>154</v>
+      </c>
+      <c r="AB23" s="84" t="s">
         <v>32</v>
-      </c>
-      <c r="Z23" s="26" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA23" s="81" t="s">
-        <v>163</v>
-      </c>
-      <c r="AB23" s="84" t="s">
-        <v>39</v>
       </c>
       <c r="AC23" s="41"/>
       <c r="AD23" s="43" t="s">
+        <v>106</v>
+      </c>
+      <c r="AE23" s="43" t="s">
+        <v>107</v>
+      </c>
+      <c r="AF23" s="43" t="s">
+        <v>108</v>
+      </c>
+      <c r="AG23" s="43" t="s">
+        <v>109</v>
+      </c>
+      <c r="AH23" s="43" t="s">
+        <v>110</v>
+      </c>
+      <c r="AI23" s="43" t="s">
+        <v>111</v>
+      </c>
+      <c r="AJ23" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="AK23" s="43" t="s">
         <v>113</v>
       </c>
-      <c r="AE23" s="43" t="s">
+      <c r="AL23" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="AF23" s="43" t="s">
+      <c r="AM23" s="43" t="s">
         <v>115</v>
       </c>
-      <c r="AG23" s="43" t="s">
+      <c r="AN23" s="43" t="s">
         <v>116</v>
-      </c>
-      <c r="AH23" s="43" t="s">
-        <v>117</v>
-      </c>
-      <c r="AI23" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="AJ23" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="AK23" s="43" t="s">
-        <v>120</v>
-      </c>
-      <c r="AL23" s="43" t="s">
-        <v>121</v>
-      </c>
-      <c r="AM23" s="43" t="s">
-        <v>122</v>
-      </c>
-      <c r="AN23" s="43" t="s">
-        <v>123</v>
       </c>
       <c r="AO23" s="47"/>
       <c r="AP23" s="69" t="s">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="AQ23" s="70" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="AR23" s="71" t="s">
-        <v>140</v>
+        <v>133</v>
       </c>
       <c r="AS23" s="70" t="s">
-        <v>136</v>
+        <v>129</v>
       </c>
       <c r="AT23" s="71" t="s">
-        <v>142</v>
+        <v>135</v>
       </c>
       <c r="AU23" s="70" t="s">
-        <v>138</v>
+        <v>131</v>
       </c>
       <c r="AV23" s="72" t="s">
-        <v>144</v>
+        <v>137</v>
       </c>
       <c r="AW23" s="69" t="s">
-        <v>152</v>
+        <v>145</v>
       </c>
       <c r="AX23" s="70" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="AY23" s="71" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="AZ23" s="70" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="BA23" s="71" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="BB23" s="70" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="BC23" s="72" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="BE23" s="17" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="BF23" s="17" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="BG23" s="17">
         <v>1</v>
       </c>
       <c r="BH23" s="17" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="BI23" s="17" t="s">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="BJ23" s="17" t="s">
-        <v>49</v>
+        <v>42</v>
       </c>
       <c r="BK23" s="17"/>
       <c r="BL23" s="18" t="s">
-        <v>51</v>
+        <v>44</v>
       </c>
       <c r="BM23" s="18" t="s">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="BN23" s="18">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:66" ht="15.75" customHeight="1">
+    <row r="24" spans="1:66" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="D24" s="7"/>
       <c r="E24" s="7"/>
@@ -3517,32 +3493,33 @@
       <c r="BC24" s="11"/>
       <c r="BD24" s="11"/>
       <c r="BE24" s="11" t="s">
-        <v>41</v>
+        <v>34</v>
       </c>
       <c r="BF24" s="76" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
       <c r="BG24" s="11">
         <v>14</v>
       </c>
       <c r="BH24" s="11" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="BI24" s="11"/>
       <c r="BJ24" s="11"/>
       <c r="BK24" s="11"/>
     </row>
-    <row r="25" spans="1:66" s="101" customFormat="1" ht="18.75"/>
-    <row r="26" spans="1:66" s="102" customFormat="1" ht="15.75" customHeight="1">
+    <row r="25" spans="1:66" s="101" customFormat="1" ht="18.75" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="1:66" s="102" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="L26" s="103"/>
       <c r="O26" s="104"/>
       <c r="R26" s="103"/>
       <c r="U26" s="103"/>
     </row>
-    <row r="27" spans="1:66" s="102" customFormat="1" ht="15.75" customHeight="1">
-      <c r="B27" s="105" t="s">
-        <v>15</v>
-      </c>
+    <row r="27" spans="1:66" s="102" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="102" t="s">
+        <v>156</v>
+      </c>
+      <c r="B27" s="105"/>
       <c r="C27" s="105"/>
       <c r="D27" s="105"/>
       <c r="E27" s="105"/>
@@ -3560,14 +3537,10 @@
       <c r="Q27" s="107"/>
       <c r="R27" s="105"/>
       <c r="T27" s="106"/>
-      <c r="U27" s="108" t="s">
-        <v>17</v>
-      </c>
+      <c r="U27" s="108"/>
     </row>
-    <row r="28" spans="1:66" s="102" customFormat="1" ht="15.75" customHeight="1">
-      <c r="B28" s="105" t="s">
-        <v>16</v>
-      </c>
+    <row r="28" spans="1:66" s="102" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B28" s="105"/>
       <c r="C28" s="105"/>
       <c r="D28" s="105"/>
       <c r="E28" s="105"/>
@@ -3584,17 +3557,9 @@
       <c r="P28" s="108"/>
       <c r="Q28" s="105"/>
       <c r="T28" s="108"/>
-      <c r="U28" s="102" t="s">
-        <v>18</v>
-      </c>
-      <c r="X28" s="102" t="s">
-        <v>160</v>
-      </c>
     </row>
-    <row r="29" spans="1:66" s="102" customFormat="1" ht="15.75" customHeight="1">
-      <c r="B29" s="105" t="s">
-        <v>2</v>
-      </c>
+    <row r="29" spans="1:66" s="102" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B29" s="105"/>
       <c r="C29" s="105"/>
       <c r="D29" s="105"/>
       <c r="E29" s="105"/>
@@ -3611,8 +3576,14 @@
       <c r="P29" s="105"/>
       <c r="Q29" s="105"/>
       <c r="T29" s="105"/>
+      <c r="AG29" s="102" t="s">
+        <v>159</v>
+      </c>
     </row>
-    <row r="30" spans="1:66" s="102" customFormat="1" ht="15.75" customHeight="1">
+    <row r="30" spans="1:66" s="102" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="102" t="s">
+        <v>157</v>
+      </c>
       <c r="B30" s="105"/>
       <c r="C30" s="105"/>
       <c r="D30" s="105"/>
@@ -3630,11 +3601,15 @@
       <c r="P30" s="107"/>
       <c r="Q30" s="105"/>
       <c r="T30" s="105"/>
+      <c r="AG30" s="102" t="s">
+        <v>160</v>
+      </c>
+      <c r="AK30" s="102" t="s">
+        <v>161</v>
+      </c>
     </row>
-    <row r="31" spans="1:66" s="102" customFormat="1" ht="15.75" customHeight="1">
-      <c r="B31" s="105" t="s">
-        <v>19</v>
-      </c>
+    <row r="31" spans="1:66" s="102" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B31" s="105"/>
       <c r="C31" s="105"/>
       <c r="D31" s="105"/>
       <c r="E31" s="105"/>
@@ -3651,14 +3626,11 @@
       <c r="P31" s="108"/>
       <c r="Q31" s="106"/>
       <c r="T31" s="105"/>
-      <c r="U31" s="102" t="s">
-        <v>165</v>
-      </c>
-      <c r="X31" s="102" t="s">
-        <v>161</v>
-      </c>
     </row>
-    <row r="32" spans="1:66" s="102" customFormat="1" ht="15.75" customHeight="1">
+    <row r="32" spans="1:66" s="102" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="102" t="s">
+        <v>13</v>
+      </c>
       <c r="B32" s="105"/>
       <c r="C32" s="105"/>
       <c r="D32" s="105"/>
@@ -3677,10 +3649,8 @@
       <c r="Q32" s="105"/>
       <c r="T32" s="105"/>
     </row>
-    <row r="33" spans="2:63" s="102" customFormat="1" ht="15.75" customHeight="1">
-      <c r="B33" s="105" t="s">
-        <v>20</v>
-      </c>
+    <row r="33" spans="1:63" s="102" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B33" s="105"/>
       <c r="C33" s="105"/>
       <c r="D33" s="105"/>
       <c r="E33" s="105"/>
@@ -3696,8 +3666,17 @@
       <c r="P33" s="105"/>
       <c r="Q33" s="105"/>
       <c r="T33" s="111"/>
+      <c r="AG33" s="102" t="s">
+        <v>162</v>
+      </c>
+      <c r="AK33" s="102" t="s">
+        <v>163</v>
+      </c>
     </row>
-    <row r="34" spans="2:63" s="102" customFormat="1" ht="15.75" customHeight="1">
+    <row r="34" spans="1:63" s="102" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="102" t="s">
+        <v>158</v>
+      </c>
       <c r="B34" s="105"/>
       <c r="C34" s="105"/>
       <c r="D34" s="105"/>
@@ -3709,10 +3688,8 @@
       <c r="J34" s="105"/>
       <c r="K34" s="105"/>
     </row>
-    <row r="35" spans="2:63" s="102" customFormat="1" ht="18.75">
-      <c r="B35" s="112" t="s">
-        <v>168</v>
-      </c>
+    <row r="35" spans="1:63" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B35" s="112"/>
       <c r="C35" s="105"/>
       <c r="D35" s="105"/>
       <c r="E35" s="105"/>
@@ -3723,23 +3700,23 @@
       <c r="J35" s="105"/>
       <c r="K35" s="105"/>
       <c r="T35" s="111"/>
-      <c r="U35" s="102" t="s">
-        <v>166</v>
-      </c>
-      <c r="X35" s="102" t="s">
-        <v>167</v>
+      <c r="AG35" s="102" t="s">
+        <v>164</v>
+      </c>
+      <c r="AK35" s="102" t="s">
+        <v>165</v>
       </c>
     </row>
-    <row r="36" spans="2:63" s="102" customFormat="1" ht="18.75"/>
-    <row r="37" spans="2:63" s="16" customFormat="1">
+    <row r="36" spans="1:63" s="102" customFormat="1" ht="18.75" x14ac:dyDescent="0.3"/>
+    <row r="37" spans="1:63" s="16" customFormat="1" x14ac:dyDescent="0.25">
       <c r="BI37" s="16" t="s">
-        <v>44</v>
+        <v>37</v>
       </c>
       <c r="BJ37" s="77" t="s">
-        <v>52</v>
+        <v>45</v>
       </c>
     </row>
-    <row r="38" spans="2:63">
+    <row r="38" spans="1:63" x14ac:dyDescent="0.25">
       <c r="AI38" s="11"/>
       <c r="AR38" s="11"/>
       <c r="AS38" s="11"/>
@@ -3755,7 +3732,7 @@
       <c r="BC38" s="11"/>
       <c r="BD38" s="11"/>
       <c r="BE38" s="78" t="s">
-        <v>53</v>
+        <v>46</v>
       </c>
       <c r="BF38" s="11"/>
       <c r="BG38" s="11"/>
@@ -3767,25 +3744,26 @@
   </sheetData>
   <sheetProtection formatCells="0" formatColumns="0" formatRows="0" insertColumns="0" insertRows="0" insertHyperlinks="0" deleteColumns="0" deleteRows="0" sort="0" autoFilter="0" pivotTables="0"/>
   <mergeCells count="62">
-    <mergeCell ref="A13:AA13"/>
-    <mergeCell ref="A14:AA14"/>
-    <mergeCell ref="A15:AA15"/>
-    <mergeCell ref="L16:M16"/>
-    <mergeCell ref="E17:E19"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="L17:L19"/>
-    <mergeCell ref="M17:M19"/>
-    <mergeCell ref="AK16:AL16"/>
-    <mergeCell ref="AM16:AN16"/>
-    <mergeCell ref="AE17:AE19"/>
-    <mergeCell ref="AF17:AF19"/>
-    <mergeCell ref="AG17:AG19"/>
-    <mergeCell ref="AH17:AH19"/>
-    <mergeCell ref="AK17:AK19"/>
-    <mergeCell ref="AL17:AL19"/>
-    <mergeCell ref="AM17:AM19"/>
-    <mergeCell ref="AN17:AN19"/>
+    <mergeCell ref="AD16:AD19"/>
+    <mergeCell ref="AE16:AF16"/>
+    <mergeCell ref="AG16:AH16"/>
+    <mergeCell ref="AI16:AI19"/>
+    <mergeCell ref="AJ16:AJ19"/>
+    <mergeCell ref="AP16:AV16"/>
+    <mergeCell ref="AP17:AP19"/>
+    <mergeCell ref="AQ17:AR17"/>
+    <mergeCell ref="AS17:AT17"/>
+    <mergeCell ref="AU17:AV17"/>
+    <mergeCell ref="AW16:BC16"/>
+    <mergeCell ref="AW17:AW19"/>
+    <mergeCell ref="AX17:AY17"/>
+    <mergeCell ref="AZ17:BA17"/>
+    <mergeCell ref="BB17:BC17"/>
+    <mergeCell ref="E16:K16"/>
+    <mergeCell ref="T17:T19"/>
+    <mergeCell ref="H18:H19"/>
+    <mergeCell ref="K18:K19"/>
+    <mergeCell ref="AB16:AB19"/>
     <mergeCell ref="A22:B22"/>
     <mergeCell ref="A23:B23"/>
     <mergeCell ref="R17:R19"/>
@@ -3797,38 +3775,37 @@
     <mergeCell ref="O18:O19"/>
     <mergeCell ref="P18:P19"/>
     <mergeCell ref="Q18:Q19"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="B16:B19"/>
+    <mergeCell ref="C17:C19"/>
+    <mergeCell ref="D17:D19"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="AK16:AL16"/>
+    <mergeCell ref="AM16:AN16"/>
+    <mergeCell ref="AE17:AE19"/>
+    <mergeCell ref="AF17:AF19"/>
+    <mergeCell ref="AG17:AG19"/>
+    <mergeCell ref="AH17:AH19"/>
+    <mergeCell ref="AK17:AK19"/>
+    <mergeCell ref="AL17:AL19"/>
+    <mergeCell ref="AM17:AM19"/>
+    <mergeCell ref="AN17:AN19"/>
+    <mergeCell ref="A13:AA13"/>
+    <mergeCell ref="A14:AA14"/>
+    <mergeCell ref="A15:AA15"/>
+    <mergeCell ref="L16:M16"/>
+    <mergeCell ref="E17:E19"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="L17:L19"/>
+    <mergeCell ref="M17:M19"/>
     <mergeCell ref="U17:U19"/>
     <mergeCell ref="V17:V19"/>
     <mergeCell ref="Z16:Z19"/>
     <mergeCell ref="AA16:AA19"/>
-    <mergeCell ref="A16:A19"/>
-    <mergeCell ref="B16:B19"/>
     <mergeCell ref="W16:W19"/>
     <mergeCell ref="X16:X19"/>
     <mergeCell ref="Y16:Y19"/>
-    <mergeCell ref="C17:C19"/>
-    <mergeCell ref="D17:D19"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="E16:K16"/>
-    <mergeCell ref="T17:T19"/>
-    <mergeCell ref="H18:H19"/>
-    <mergeCell ref="K18:K19"/>
-    <mergeCell ref="AB16:AB19"/>
-    <mergeCell ref="AW16:BC16"/>
-    <mergeCell ref="AW17:AW19"/>
-    <mergeCell ref="AX17:AY17"/>
-    <mergeCell ref="AZ17:BA17"/>
-    <mergeCell ref="BB17:BC17"/>
-    <mergeCell ref="AP16:AV16"/>
-    <mergeCell ref="AP17:AP19"/>
-    <mergeCell ref="AQ17:AR17"/>
-    <mergeCell ref="AS17:AT17"/>
-    <mergeCell ref="AU17:AV17"/>
-    <mergeCell ref="AD16:AD19"/>
-    <mergeCell ref="AE16:AF16"/>
-    <mergeCell ref="AG16:AH16"/>
-    <mergeCell ref="AI16:AI19"/>
-    <mergeCell ref="AJ16:AJ19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
